--- a/dst/dst.xlsx
+++ b/dst/dst.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="17030"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\havranek\Dropbox\hermandominik_bakalarska_prace\paper\online\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19485" windowHeight="6915"/>
   </bookViews>
